--- a/backend/data/financials_by_company/002434.SZ.xlsx
+++ b/backend/data/financials_by_company/002434.SZ.xlsx
@@ -692,231 +692,231 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-3501190.845167</v>
+        <v>-267608538.6025</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09325899999999999</v>
+        <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>887698911.37</v>
+        <v>871485107.04</v>
       </c>
       <c r="E2" t="n">
-        <v>-37542511.22</v>
+        <v>-1070434154.41</v>
       </c>
       <c r="F2" t="n">
-        <v>-37542511.22</v>
+        <v>-1070434154.41</v>
       </c>
       <c r="G2" t="n">
-        <v>239986990.76</v>
+        <v>-774721316.1900001</v>
       </c>
       <c r="H2" t="n">
-        <v>495584956.33</v>
+        <v>515936607.92</v>
       </c>
       <c r="I2" t="n">
-        <v>5094850259.94</v>
+        <v>4558113103.63</v>
       </c>
       <c r="J2" t="n">
-        <v>850156400.15</v>
+        <v>-198949047.37</v>
       </c>
       <c r="K2" t="n">
-        <v>354571443.82</v>
+        <v>-714885655.29</v>
       </c>
       <c r="L2" t="n">
-        <v>-66810791.09</v>
+        <v>-60241459.16</v>
       </c>
       <c r="M2" t="n">
-        <v>71376394.25</v>
+        <v>67523528.48</v>
       </c>
       <c r="N2" t="n">
-        <v>5097716.97</v>
+        <v>10001176.45</v>
       </c>
       <c r="O2" t="n">
-        <v>274028311.134833</v>
+        <v>28104299.6175</v>
       </c>
       <c r="P2" t="n">
-        <v>239986990.76</v>
+        <v>-774721316.1900001</v>
       </c>
       <c r="Q2" t="n">
-        <v>5625140812.42</v>
+        <v>5091851364.84</v>
       </c>
       <c r="R2" t="n">
-        <v>5199125.31</v>
+        <v>8016140.69</v>
       </c>
       <c r="S2" t="n">
-        <v>287323105.32</v>
+        <v>-779592433.78</v>
       </c>
       <c r="T2" t="n">
-        <v>1333261060</v>
+        <v>1313086977</v>
       </c>
       <c r="U2" t="n">
-        <v>1333261060</v>
+        <v>1313086977</v>
       </c>
       <c r="V2" t="n">
-        <v>0.18</v>
+        <v>-0.59</v>
       </c>
       <c r="W2" t="n">
-        <v>0.18</v>
+        <v>-0.59</v>
       </c>
       <c r="X2" t="n">
-        <v>239986990.76</v>
+        <v>-774721316.1900001</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>239986990.76</v>
+        <v>-774721316.1900001</v>
       </c>
       <c r="AA2" t="n">
-        <v>-16797467.65</v>
+        <v>8566427.35</v>
       </c>
       <c r="AB2" t="n">
-        <v>256784458.41</v>
+        <v>-783287743.54</v>
       </c>
       <c r="AC2" t="n">
-        <v>256784458.41</v>
+        <v>-783287743.54</v>
       </c>
       <c r="AD2" t="n">
-        <v>26410591.16</v>
+        <v>878559.77</v>
       </c>
       <c r="AE2" t="n">
-        <v>283195049.57</v>
+        <v>-782409183.77</v>
       </c>
       <c r="AF2" t="n">
-        <v>-4128055.75</v>
+        <v>-3231801.94</v>
       </c>
       <c r="AG2" t="n">
-        <v>-38247281.22</v>
+        <v>-1069300087.41</v>
       </c>
       <c r="AH2" t="n">
-        <v>-2686694.53</v>
+        <v>9356377.92</v>
       </c>
       <c r="AI2" t="n">
-        <v>17787293.34</v>
+        <v>73526633.48</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23146682.41</v>
+        <v>986417076.01</v>
       </c>
       <c r="AK2" t="n">
-        <v>-66810791.09</v>
+        <v>-60241459.16</v>
       </c>
       <c r="AL2" t="n">
-        <v>532113.8100000001</v>
+        <v>2719107.13</v>
       </c>
       <c r="AM2" t="n">
-        <v>71376394.25</v>
+        <v>67523528.48</v>
       </c>
       <c r="AN2" t="n">
-        <v>5097716.97</v>
+        <v>10001176.45</v>
       </c>
       <c r="AO2" t="n">
-        <v>387670275.05</v>
+        <v>394900178.74</v>
       </c>
       <c r="AP2" t="n">
-        <v>530290552.48</v>
+        <v>533738261.21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>74568915.04000001</v>
+        <v>36983126.26</v>
       </c>
       <c r="AR2" t="n">
-        <v>35691118.82</v>
+        <v>33427087.55</v>
       </c>
       <c r="AS2" t="n">
-        <v>35691118.82</v>
+        <v>33427087.55</v>
       </c>
       <c r="AT2" t="n">
-        <v>304710875.48</v>
+        <v>356867606.24</v>
       </c>
       <c r="AU2" t="n">
-        <v>104095437.27</v>
+        <v>133439768.22</v>
       </c>
       <c r="AV2" t="n">
-        <v>42544884.04</v>
+        <v>94629279.84999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>61550553.23</v>
+        <v>38810488.37</v>
       </c>
       <c r="AX2" t="n">
-        <v>5199125.31</v>
+        <v>8016140.69</v>
       </c>
       <c r="AY2" t="n">
-        <v>917960827.53</v>
+        <v>928638439.95</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5094850259.94</v>
+        <v>4558113103.63</v>
       </c>
       <c r="BA2" t="n">
-        <v>6012811087.47</v>
+        <v>5486751543.58</v>
       </c>
       <c r="BB2" t="n">
-        <v>6012811087.47</v>
+        <v>5486751543.58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-7031983.56389</v>
+        <v>-8858618.775</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07896</v>
+        <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>903950118.14</v>
+        <v>830833148.12</v>
       </c>
       <c r="E3" t="n">
-        <v>-89057890.38</v>
+        <v>-35434475.1</v>
       </c>
       <c r="F3" t="n">
-        <v>-89057890.38</v>
+        <v>-35434475.1</v>
       </c>
       <c r="G3" t="n">
-        <v>301095015.96</v>
+        <v>300107069.38</v>
       </c>
       <c r="H3" t="n">
-        <v>441428285.64</v>
+        <v>434791667.28</v>
       </c>
       <c r="I3" t="n">
-        <v>4947865784.78</v>
+        <v>4236820209.85</v>
       </c>
       <c r="J3" t="n">
-        <v>814892227.76</v>
+        <v>795398673.02</v>
       </c>
       <c r="K3" t="n">
-        <v>373463942.12</v>
+        <v>360607005.74</v>
       </c>
       <c r="L3" t="n">
-        <v>-48474289.29</v>
+        <v>-51617853.16</v>
       </c>
       <c r="M3" t="n">
-        <v>54575770.8</v>
+        <v>61541972.93</v>
       </c>
       <c r="N3" t="n">
-        <v>7120275.9</v>
+        <v>11112537.08</v>
       </c>
       <c r="O3" t="n">
-        <v>383120922.77611</v>
+        <v>326682925.705</v>
       </c>
       <c r="P3" t="n">
-        <v>301095015.96</v>
+        <v>300107069.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>5452945161</v>
+        <v>4735692872.34</v>
       </c>
       <c r="R3" t="n">
-        <v>5356627.6</v>
+        <v>5125240.3</v>
       </c>
       <c r="S3" t="n">
-        <v>327581610.12</v>
+        <v>299692027.73</v>
       </c>
       <c r="T3" t="n">
-        <v>1309108765</v>
+        <v>1304813345</v>
       </c>
       <c r="U3" t="n">
-        <v>1309108765</v>
+        <v>1304813345</v>
       </c>
       <c r="V3" t="n">
         <v>0.23</v>
@@ -925,162 +925,162 @@
         <v>0.23</v>
       </c>
       <c r="X3" t="n">
-        <v>301095015.96</v>
+        <v>300107069.38</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>301095015.96</v>
+        <v>300107069.38</v>
       </c>
       <c r="AA3" t="n">
-        <v>7386156.32</v>
+        <v>105578.69</v>
       </c>
       <c r="AB3" t="n">
-        <v>293708859.64</v>
+        <v>300001490.69</v>
       </c>
       <c r="AC3" t="n">
-        <v>293708859.64</v>
+        <v>300001490.69</v>
       </c>
       <c r="AD3" t="n">
-        <v>25179311.68</v>
+        <v>-936457.88</v>
       </c>
       <c r="AE3" t="n">
-        <v>318888171.32</v>
+        <v>299065032.81</v>
       </c>
       <c r="AF3" t="n">
-        <v>-8693438.800000001</v>
+        <v>-626994.92</v>
       </c>
       <c r="AG3" t="n">
-        <v>-88878494.38</v>
+        <v>-33941644.1</v>
       </c>
       <c r="AH3" t="n">
-        <v>-28997696.35</v>
+        <v>-7966888.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>17575140.55</v>
+        <v>36469335.63</v>
       </c>
       <c r="AJ3" t="n">
-        <v>100301050.18</v>
+        <v>5439196.97</v>
       </c>
       <c r="AK3" t="n">
-        <v>-48474289.29</v>
+        <v>-51617853.16</v>
       </c>
       <c r="AL3" t="n">
-        <v>1018794.39</v>
+        <v>1188417.31</v>
       </c>
       <c r="AM3" t="n">
-        <v>54575770.8</v>
+        <v>61541972.93</v>
       </c>
       <c r="AN3" t="n">
-        <v>7120275.9</v>
+        <v>11112537.08</v>
       </c>
       <c r="AO3" t="n">
-        <v>459814213.5</v>
+        <v>377442901.37</v>
       </c>
       <c r="AP3" t="n">
-        <v>505079376.22</v>
+        <v>498872662.49</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-51467664.82</v>
+        <v>29261641.62</v>
       </c>
       <c r="AR3" t="n">
-        <v>32831614.71</v>
+        <v>33567468.04</v>
       </c>
       <c r="AS3" t="n">
-        <v>32831614.71</v>
+        <v>33567468.04</v>
       </c>
       <c r="AT3" t="n">
-        <v>348557744.99</v>
+        <v>333302806.35</v>
       </c>
       <c r="AU3" t="n">
-        <v>168629910.54</v>
+        <v>172881282.48</v>
       </c>
       <c r="AV3" t="n">
-        <v>117076833.11</v>
+        <v>132452103.98</v>
       </c>
       <c r="AW3" t="n">
-        <v>51553077.43</v>
+        <v>40429178.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>5356627.6</v>
+        <v>5125240.3</v>
       </c>
       <c r="AY3" t="n">
-        <v>964893589.72</v>
+        <v>876315563.86</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4947865784.78</v>
+        <v>4236820209.85</v>
       </c>
       <c r="BA3" t="n">
-        <v>5912759374.5</v>
+        <v>5113135773.71</v>
       </c>
       <c r="BB3" t="n">
-        <v>5912759374.5</v>
+        <v>5113135773.71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-8858618.775</v>
+        <v>-7031983.56389</v>
       </c>
       <c r="C4" t="n">
-        <v>0.25</v>
+        <v>0.07896</v>
       </c>
       <c r="D4" t="n">
-        <v>830833148.12</v>
+        <v>903950118.14</v>
       </c>
       <c r="E4" t="n">
-        <v>-35434475.1</v>
+        <v>-89057890.38</v>
       </c>
       <c r="F4" t="n">
-        <v>-35434475.1</v>
+        <v>-89057890.38</v>
       </c>
       <c r="G4" t="n">
-        <v>300107069.38</v>
+        <v>301095015.96</v>
       </c>
       <c r="H4" t="n">
-        <v>434791667.28</v>
+        <v>441428285.64</v>
       </c>
       <c r="I4" t="n">
-        <v>4236820209.85</v>
+        <v>4947865784.78</v>
       </c>
       <c r="J4" t="n">
-        <v>795398673.02</v>
+        <v>814892227.76</v>
       </c>
       <c r="K4" t="n">
-        <v>360607005.74</v>
+        <v>373463942.12</v>
       </c>
       <c r="L4" t="n">
-        <v>-51617853.16</v>
+        <v>-48474289.29</v>
       </c>
       <c r="M4" t="n">
-        <v>61541972.93</v>
+        <v>54575770.8</v>
       </c>
       <c r="N4" t="n">
-        <v>11112537.08</v>
+        <v>7120275.9</v>
       </c>
       <c r="O4" t="n">
-        <v>326682925.705</v>
+        <v>383120922.77611</v>
       </c>
       <c r="P4" t="n">
-        <v>300107069.38</v>
+        <v>301095015.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>4735692872.34</v>
+        <v>5452945161</v>
       </c>
       <c r="R4" t="n">
-        <v>5125240.3</v>
+        <v>5356627.6</v>
       </c>
       <c r="S4" t="n">
-        <v>299692027.73</v>
+        <v>327581610.12</v>
       </c>
       <c r="T4" t="n">
-        <v>1304813345</v>
+        <v>1309108765</v>
       </c>
       <c r="U4" t="n">
-        <v>1304813345</v>
+        <v>1309108765</v>
       </c>
       <c r="V4" t="n">
         <v>0.23</v>
@@ -1089,261 +1089,261 @@
         <v>0.23</v>
       </c>
       <c r="X4" t="n">
-        <v>300107069.38</v>
+        <v>301095015.96</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>300107069.38</v>
+        <v>301095015.96</v>
       </c>
       <c r="AA4" t="n">
-        <v>105578.69</v>
+        <v>7386156.32</v>
       </c>
       <c r="AB4" t="n">
-        <v>300001490.69</v>
+        <v>293708859.64</v>
       </c>
       <c r="AC4" t="n">
-        <v>300001490.69</v>
+        <v>293708859.64</v>
       </c>
       <c r="AD4" t="n">
-        <v>-936457.88</v>
+        <v>25179311.68</v>
       </c>
       <c r="AE4" t="n">
-        <v>299065032.81</v>
+        <v>318888171.32</v>
       </c>
       <c r="AF4" t="n">
-        <v>-626994.92</v>
+        <v>-8693438.800000001</v>
       </c>
       <c r="AG4" t="n">
-        <v>-33941644.1</v>
+        <v>-88878494.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>-7966888.5</v>
+        <v>-28997696.35</v>
       </c>
       <c r="AI4" t="n">
-        <v>36469335.63</v>
+        <v>17575140.55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5439196.97</v>
+        <v>100301050.18</v>
       </c>
       <c r="AK4" t="n">
-        <v>-51617853.16</v>
+        <v>-48474289.29</v>
       </c>
       <c r="AL4" t="n">
-        <v>1188417.31</v>
+        <v>1018794.39</v>
       </c>
       <c r="AM4" t="n">
-        <v>61541972.93</v>
+        <v>54575770.8</v>
       </c>
       <c r="AN4" t="n">
-        <v>11112537.08</v>
+        <v>7120275.9</v>
       </c>
       <c r="AO4" t="n">
-        <v>377442901.37</v>
+        <v>459814213.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>498872662.49</v>
+        <v>505079376.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>29261641.62</v>
+        <v>-51467664.82</v>
       </c>
       <c r="AR4" t="n">
-        <v>33567468.04</v>
+        <v>32831614.71</v>
       </c>
       <c r="AS4" t="n">
-        <v>33567468.04</v>
+        <v>32831614.71</v>
       </c>
       <c r="AT4" t="n">
-        <v>333302806.35</v>
+        <v>348557744.99</v>
       </c>
       <c r="AU4" t="n">
-        <v>172881282.48</v>
+        <v>168629910.54</v>
       </c>
       <c r="AV4" t="n">
-        <v>132452103.98</v>
+        <v>117076833.11</v>
       </c>
       <c r="AW4" t="n">
-        <v>40429178.5</v>
+        <v>51553077.43</v>
       </c>
       <c r="AX4" t="n">
-        <v>5125240.3</v>
+        <v>5356627.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>876315563.86</v>
+        <v>964893589.72</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4236820209.85</v>
+        <v>4947865784.78</v>
       </c>
       <c r="BA4" t="n">
-        <v>5113135773.71</v>
+        <v>5912759374.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>5113135773.71</v>
+        <v>5912759374.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-267608538.6025</v>
+        <v>-3501190.845167</v>
       </c>
       <c r="C5" t="n">
-        <v>0.25</v>
+        <v>0.09325899999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>871485107.04</v>
+        <v>887698911.37</v>
       </c>
       <c r="E5" t="n">
-        <v>-1070434154.41</v>
+        <v>-37542511.22</v>
       </c>
       <c r="F5" t="n">
-        <v>-1070434154.41</v>
+        <v>-37542511.22</v>
       </c>
       <c r="G5" t="n">
-        <v>-774721316.1900001</v>
+        <v>239986990.76</v>
       </c>
       <c r="H5" t="n">
-        <v>515936607.92</v>
+        <v>495584956.33</v>
       </c>
       <c r="I5" t="n">
-        <v>4558113103.63</v>
+        <v>5094850259.94</v>
       </c>
       <c r="J5" t="n">
-        <v>-198949047.37</v>
+        <v>850156400.15</v>
       </c>
       <c r="K5" t="n">
-        <v>-714885655.29</v>
+        <v>354571443.82</v>
       </c>
       <c r="L5" t="n">
-        <v>-60241459.16</v>
+        <v>-66810791.09</v>
       </c>
       <c r="M5" t="n">
-        <v>67523528.48</v>
+        <v>71376394.25</v>
       </c>
       <c r="N5" t="n">
-        <v>10001176.45</v>
+        <v>5097716.97</v>
       </c>
       <c r="O5" t="n">
-        <v>28104299.6175</v>
+        <v>274028311.134833</v>
       </c>
       <c r="P5" t="n">
-        <v>-774721316.1900001</v>
+        <v>239986990.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>5091851364.84</v>
+        <v>5625140812.42</v>
       </c>
       <c r="R5" t="n">
-        <v>8016140.69</v>
+        <v>5199125.31</v>
       </c>
       <c r="S5" t="n">
-        <v>-779592433.78</v>
+        <v>287323105.32</v>
       </c>
       <c r="T5" t="n">
-        <v>1313086977</v>
+        <v>1333261060</v>
       </c>
       <c r="U5" t="n">
-        <v>1313086977</v>
+        <v>1333261060</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.59</v>
+        <v>0.18</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.59</v>
+        <v>0.18</v>
       </c>
       <c r="X5" t="n">
-        <v>-774721316.1900001</v>
+        <v>239986990.76</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-774721316.1900001</v>
+        <v>239986990.76</v>
       </c>
       <c r="AA5" t="n">
-        <v>8566427.35</v>
+        <v>-16797467.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>-783287743.54</v>
+        <v>256784458.41</v>
       </c>
       <c r="AC5" t="n">
-        <v>-783287743.54</v>
+        <v>256784458.41</v>
       </c>
       <c r="AD5" t="n">
-        <v>878559.77</v>
+        <v>26410591.16</v>
       </c>
       <c r="AE5" t="n">
-        <v>-782409183.77</v>
+        <v>283195049.57</v>
       </c>
       <c r="AF5" t="n">
-        <v>-3231801.94</v>
+        <v>-4128055.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1069300087.41</v>
+        <v>-38247281.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>9356377.92</v>
+        <v>-2686694.53</v>
       </c>
       <c r="AI5" t="n">
-        <v>73526633.48</v>
+        <v>17787293.34</v>
       </c>
       <c r="AJ5" t="n">
-        <v>986417076.01</v>
+        <v>23146682.41</v>
       </c>
       <c r="AK5" t="n">
-        <v>-60241459.16</v>
+        <v>-66810791.09</v>
       </c>
       <c r="AL5" t="n">
-        <v>2719107.13</v>
+        <v>532113.8100000001</v>
       </c>
       <c r="AM5" t="n">
-        <v>67523528.48</v>
+        <v>71376394.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>10001176.45</v>
+        <v>5097716.97</v>
       </c>
       <c r="AO5" t="n">
-        <v>394900178.74</v>
+        <v>387670275.05</v>
       </c>
       <c r="AP5" t="n">
-        <v>533738261.21</v>
+        <v>530290552.48</v>
       </c>
       <c r="AQ5" t="n">
-        <v>36983126.26</v>
+        <v>74568915.04000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>33427087.55</v>
+        <v>35691118.82</v>
       </c>
       <c r="AS5" t="n">
-        <v>33427087.55</v>
+        <v>35691118.82</v>
       </c>
       <c r="AT5" t="n">
-        <v>356867606.24</v>
+        <v>304710875.48</v>
       </c>
       <c r="AU5" t="n">
-        <v>133439768.22</v>
+        <v>104095437.27</v>
       </c>
       <c r="AV5" t="n">
-        <v>94629279.84999999</v>
+        <v>42544884.04</v>
       </c>
       <c r="AW5" t="n">
-        <v>38810488.37</v>
+        <v>61550553.23</v>
       </c>
       <c r="AX5" t="n">
-        <v>8016140.69</v>
+        <v>5199125.31</v>
       </c>
       <c r="AY5" t="n">
-        <v>928638439.95</v>
+        <v>917960827.53</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4558113103.63</v>
+        <v>5094850259.94</v>
       </c>
       <c r="BA5" t="n">
-        <v>5486751543.58</v>
+        <v>6012811087.47</v>
       </c>
       <c r="BB5" t="n">
-        <v>5486751543.58</v>
+        <v>6012811087.47</v>
       </c>
     </row>
   </sheetData>
@@ -1734,90 +1734,228 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46022</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1340000000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1340000000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>977466987.04</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1904681921.32</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4650812478.51</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7246396567.4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>322144080.51</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4650812478.51</v>
+      </c>
+      <c r="J2" t="n">
+        <v>35677.49</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5395097222.19</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5490205235.89</v>
+      </c>
+      <c r="M2" t="n">
+        <v>5445559336.9</v>
+      </c>
+      <c r="N2" t="n">
+        <v>50462114.71</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5395097222.19</v>
+      </c>
+      <c r="P2" t="n">
+        <v>205142925.63</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>848311577.9299999</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3036005321.44</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1340000000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1340000000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4679491912.57</v>
+      </c>
+      <c r="V2" t="n">
+        <v>363964875.35</v>
+      </c>
+      <c r="W2" t="n">
+        <v>56485350.09</v>
+      </c>
+      <c r="X2" t="n">
+        <v>27412920</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>179755037.43</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>5167876.64</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>95143691.19</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>35677.49</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>95108013.7</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4315527037.22</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1938255.56</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1809538230.13</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1756191331.51</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2489140893.42</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>76256102.13</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>34216326.53</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>82053359.86</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2296615104.9</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>10125051249.47</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>5487380131.74</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>291497174.48</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>11410811.61</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>110109739.35</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>117150000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>117150000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>552880133.85</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>260455014.68</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>744284743.6799999</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>487779798.66</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>256504945.02</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3091877196.2</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-1891950756.03</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>4983827952.23</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>419131988.85</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>3926823149.85</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>18820356.64</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>619052456.89</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>4637671117.73</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>155332065.32</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>42720183.29</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>932873049.14</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0</v>
+      </c>
       <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="n">
-        <v>-149134643.84</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1315417481.43</v>
-      </c>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr"/>
-      <c r="BW2" t="inlineStr"/>
+      <c r="BL2" t="n">
+        <v>316922387.24</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>241965741.08</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>373984920.82</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1074642462.71</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1554305066.1</v>
+      </c>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="n">
+        <v>877798291.17</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>3965933</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>873832358.17</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>394584329.02</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>414208061.13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45657</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1312600000</v>
@@ -1826,44 +1964,44 @@
         <v>1312600000</v>
       </c>
       <c r="D3" t="n">
-        <v>1258272376.06</v>
+        <v>903313807.7</v>
       </c>
       <c r="E3" t="n">
-        <v>2371386797.12</v>
+        <v>1592787869.41</v>
       </c>
       <c r="F3" t="n">
-        <v>4936088333.13</v>
+        <v>4839442370.14</v>
       </c>
       <c r="G3" t="n">
-        <v>7729972810.12</v>
+        <v>7179183712.17</v>
       </c>
       <c r="H3" t="n">
-        <v>477837043.28</v>
+        <v>736638381.71</v>
       </c>
       <c r="I3" t="n">
-        <v>4936088333.13</v>
+        <v>4839442370.14</v>
       </c>
       <c r="J3" t="n">
-        <v>37344044.49</v>
+        <v>2760795.09</v>
       </c>
       <c r="K3" t="n">
-        <v>5739908569.81</v>
+        <v>5592606563.09</v>
       </c>
       <c r="L3" t="n">
-        <v>6342447068.55</v>
+        <v>5792709713.77</v>
       </c>
       <c r="M3" t="n">
-        <v>5845332715.64</v>
+        <v>5601386607.59</v>
       </c>
       <c r="N3" t="n">
-        <v>105424145.83</v>
+        <v>8780044.5</v>
       </c>
       <c r="O3" t="n">
-        <v>5739908569.81</v>
+        <v>5592606563.09</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>1278666320.45</v>
+        <v>1148418647.31</v>
       </c>
       <c r="R3" t="n">
         <v>2840834667.33</v>
@@ -1875,165 +2013,165 @@
         <v>1312600000</v>
       </c>
       <c r="U3" t="n">
-        <v>4826611351.97</v>
+        <v>4489471164.79</v>
       </c>
       <c r="V3" t="n">
-        <v>967216854.6799999</v>
+        <v>525326985.47</v>
       </c>
       <c r="W3" t="n">
-        <v>30800040.52</v>
+        <v>52802379.38</v>
       </c>
       <c r="X3" t="n">
-        <v>27365000</v>
+        <v>37278240</v>
       </c>
       <c r="Y3" t="n">
-        <v>259553443.55</v>
+        <v>227935390.65</v>
       </c>
       <c r="Z3" t="n">
-        <v>9615827.380000001</v>
+        <v>4447029.67</v>
       </c>
       <c r="AA3" t="n">
-        <v>639882543.23</v>
+        <v>202863945.77</v>
       </c>
       <c r="AB3" t="n">
-        <v>37344044.49</v>
+        <v>2760795.09</v>
       </c>
       <c r="AC3" t="n">
-        <v>602538498.74</v>
+        <v>200103150.68</v>
       </c>
       <c r="AD3" t="n">
-        <v>3859394497.29</v>
+        <v>3964144179.32</v>
       </c>
       <c r="AE3" t="n">
-        <v>7348051.62</v>
+        <v>1891764.79</v>
       </c>
       <c r="AF3" t="n">
-        <v>1731504253.89</v>
+        <v>1389923923.64</v>
       </c>
       <c r="AG3" t="n">
-        <v>1387525741.57</v>
+        <v>1386473998.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>2055420164.65</v>
+        <v>2557776454.23</v>
       </c>
       <c r="AI3" t="n">
-        <v>90695922.16</v>
+        <v>78080720.2</v>
       </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>79276102.62</v>
+        <v>82389953.29000001</v>
       </c>
       <c r="AL3" t="n">
-        <v>1885448139.87</v>
+        <v>2397305780.74</v>
       </c>
       <c r="AM3" t="n">
-        <v>10671944067.61</v>
+        <v>10090857772.38</v>
       </c>
       <c r="AN3" t="n">
-        <v>6334712527.04</v>
+        <v>5390075211.35</v>
       </c>
       <c r="AO3" t="n">
-        <v>257905878.53</v>
+        <v>331919744.1</v>
       </c>
       <c r="AP3" t="n">
-        <v>37177148.34</v>
+        <v>10652016.1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>220884974.07</v>
+        <v>137263034.34</v>
       </c>
       <c r="AR3" t="n">
-        <v>215150000</v>
+        <v>142150000</v>
       </c>
       <c r="AS3" t="n">
-        <v>215150000</v>
+        <v>142150000</v>
       </c>
       <c r="AT3" t="n">
-        <v>476077026.93</v>
+        <v>528065006.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>195572813.61</v>
+        <v>237606140.92</v>
       </c>
       <c r="AV3" t="n">
-        <v>803820236.6799999</v>
+        <v>753164192.95</v>
       </c>
       <c r="AW3" t="n">
-        <v>547315291.66</v>
+        <v>496659247.93</v>
       </c>
       <c r="AX3" t="n">
         <v>256504945.02</v>
       </c>
       <c r="AY3" t="n">
-        <v>3852534364.92</v>
+        <v>3028664106.71</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-2902226202.12</v>
+        <v>-2236620293.04</v>
       </c>
       <c r="BA3" t="n">
-        <v>6754760567.04</v>
+        <v>5265284399.75</v>
       </c>
       <c r="BB3" t="n">
-        <v>387465197.22</v>
+        <v>349773036.11</v>
       </c>
       <c r="BC3" t="n">
-        <v>5332109680.88</v>
+        <v>4213395081.44</v>
       </c>
       <c r="BD3" t="n">
-        <v>19952389.39</v>
+        <v>19693852.89</v>
       </c>
       <c r="BE3" t="n">
-        <v>1015233299.55</v>
+        <v>682422429.3099999</v>
       </c>
       <c r="BF3" t="n">
-        <v>4337231540.57</v>
+        <v>4700782561.03</v>
       </c>
       <c r="BG3" t="n">
-        <v>596340694.67</v>
+        <v>259493594.48</v>
       </c>
       <c r="BH3" t="n">
-        <v>50086112.28</v>
+        <v>73675758.97</v>
       </c>
       <c r="BI3" t="n">
-        <v>1099087044.24</v>
+        <v>882846169.6900001</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
       </c>
-      <c r="BK3" t="n">
-        <v>160719000</v>
-      </c>
+      <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="n">
-        <v>319320986.63</v>
+        <v>274084899.6</v>
       </c>
       <c r="BM3" t="n">
-        <v>290184536.63</v>
+        <v>238790998.52</v>
       </c>
       <c r="BN3" t="n">
-        <v>328862520.98</v>
+        <v>369970271.57</v>
       </c>
       <c r="BO3" t="n">
-        <v>241568274.1</v>
+        <v>1382435761.67</v>
       </c>
       <c r="BP3" t="n">
-        <v>1618357551.03</v>
+        <v>1416594832.84</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-165389597.55</v>
+        <v>-144788522.99</v>
       </c>
       <c r="BR3" t="n">
-        <v>1783747148.58</v>
+        <v>1561383355.83</v>
       </c>
       <c r="BS3" t="n">
-        <v>731791864.25</v>
-      </c>
-      <c r="BT3" t="inlineStr"/>
+        <v>685736443.38</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>2473102</v>
+      </c>
       <c r="BU3" t="n">
-        <v>731791864.25</v>
+        <v>683263341.38</v>
       </c>
       <c r="BV3" t="n">
-        <v>340432955.98</v>
+        <v>350781068.45</v>
       </c>
       <c r="BW3" t="n">
-        <v>391358908.27</v>
+        <v>332482272.93</v>
       </c>
     </row>
     <row r="4">
@@ -2259,7 +2397,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44926</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>1312600000</v>
@@ -2268,44 +2406,44 @@
         <v>1312600000</v>
       </c>
       <c r="D5" t="n">
-        <v>903313807.7</v>
+        <v>1258272376.06</v>
       </c>
       <c r="E5" t="n">
-        <v>1592787869.41</v>
+        <v>2371386797.12</v>
       </c>
       <c r="F5" t="n">
-        <v>4839442370.14</v>
+        <v>4936088333.13</v>
       </c>
       <c r="G5" t="n">
-        <v>7179183712.17</v>
+        <v>7729972810.12</v>
       </c>
       <c r="H5" t="n">
-        <v>736638381.71</v>
+        <v>477837043.28</v>
       </c>
       <c r="I5" t="n">
-        <v>4839442370.14</v>
+        <v>4936088333.13</v>
       </c>
       <c r="J5" t="n">
-        <v>2760795.09</v>
+        <v>37344044.49</v>
       </c>
       <c r="K5" t="n">
-        <v>5592606563.09</v>
+        <v>5739908569.81</v>
       </c>
       <c r="L5" t="n">
-        <v>5792709713.77</v>
+        <v>6342447068.55</v>
       </c>
       <c r="M5" t="n">
-        <v>5601386607.59</v>
+        <v>5845332715.64</v>
       </c>
       <c r="N5" t="n">
-        <v>8780044.5</v>
+        <v>105424145.83</v>
       </c>
       <c r="O5" t="n">
-        <v>5592606563.09</v>
+        <v>5739908569.81</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>1148418647.31</v>
+        <v>1278666320.45</v>
       </c>
       <c r="R5" t="n">
         <v>2840834667.33</v>
@@ -2317,387 +2455,249 @@
         <v>1312600000</v>
       </c>
       <c r="U5" t="n">
-        <v>4489471164.79</v>
+        <v>4826611351.97</v>
       </c>
       <c r="V5" t="n">
-        <v>525326985.47</v>
+        <v>967216854.6799999</v>
       </c>
       <c r="W5" t="n">
-        <v>52802379.38</v>
+        <v>30800040.52</v>
       </c>
       <c r="X5" t="n">
-        <v>37278240</v>
+        <v>27365000</v>
       </c>
       <c r="Y5" t="n">
-        <v>227935390.65</v>
+        <v>259553443.55</v>
       </c>
       <c r="Z5" t="n">
-        <v>4447029.67</v>
+        <v>9615827.380000001</v>
       </c>
       <c r="AA5" t="n">
-        <v>202863945.77</v>
+        <v>639882543.23</v>
       </c>
       <c r="AB5" t="n">
-        <v>2760795.09</v>
+        <v>37344044.49</v>
       </c>
       <c r="AC5" t="n">
-        <v>200103150.68</v>
+        <v>602538498.74</v>
       </c>
       <c r="AD5" t="n">
-        <v>3964144179.32</v>
+        <v>3859394497.29</v>
       </c>
       <c r="AE5" t="n">
-        <v>1891764.79</v>
+        <v>7348051.62</v>
       </c>
       <c r="AF5" t="n">
-        <v>1389923923.64</v>
+        <v>1731504253.89</v>
       </c>
       <c r="AG5" t="n">
-        <v>1386473998.4</v>
+        <v>1387525741.57</v>
       </c>
       <c r="AH5" t="n">
-        <v>2557776454.23</v>
+        <v>2055420164.65</v>
       </c>
       <c r="AI5" t="n">
-        <v>78080720.2</v>
+        <v>90695922.16</v>
       </c>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>82389953.29000001</v>
+        <v>79276102.62</v>
       </c>
       <c r="AL5" t="n">
-        <v>2397305780.74</v>
+        <v>1885448139.87</v>
       </c>
       <c r="AM5" t="n">
-        <v>10090857772.38</v>
+        <v>10671944067.61</v>
       </c>
       <c r="AN5" t="n">
-        <v>5390075211.35</v>
+        <v>6334712527.04</v>
       </c>
       <c r="AO5" t="n">
-        <v>331919744.1</v>
+        <v>257905878.53</v>
       </c>
       <c r="AP5" t="n">
-        <v>10652016.1</v>
+        <v>37177148.34</v>
       </c>
       <c r="AQ5" t="n">
-        <v>137263034.34</v>
+        <v>220884974.07</v>
       </c>
       <c r="AR5" t="n">
-        <v>142150000</v>
+        <v>215150000</v>
       </c>
       <c r="AS5" t="n">
-        <v>142150000</v>
+        <v>215150000</v>
       </c>
       <c r="AT5" t="n">
-        <v>528065006.6</v>
+        <v>476077026.93</v>
       </c>
       <c r="AU5" t="n">
-        <v>237606140.92</v>
+        <v>195572813.61</v>
       </c>
       <c r="AV5" t="n">
-        <v>753164192.95</v>
+        <v>803820236.6799999</v>
       </c>
       <c r="AW5" t="n">
-        <v>496659247.93</v>
+        <v>547315291.66</v>
       </c>
       <c r="AX5" t="n">
         <v>256504945.02</v>
       </c>
       <c r="AY5" t="n">
-        <v>3028664106.71</v>
+        <v>3852534364.92</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-2236620293.04</v>
+        <v>-2902226202.12</v>
       </c>
       <c r="BA5" t="n">
-        <v>5265284399.75</v>
+        <v>6754760567.04</v>
       </c>
       <c r="BB5" t="n">
-        <v>349773036.11</v>
+        <v>387465197.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>4213395081.44</v>
+        <v>5332109680.88</v>
       </c>
       <c r="BD5" t="n">
-        <v>19693852.89</v>
+        <v>19952389.39</v>
       </c>
       <c r="BE5" t="n">
-        <v>682422429.3099999</v>
+        <v>1015233299.55</v>
       </c>
       <c r="BF5" t="n">
-        <v>4700782561.03</v>
+        <v>4337231540.57</v>
       </c>
       <c r="BG5" t="n">
-        <v>259493594.48</v>
+        <v>596340694.67</v>
       </c>
       <c r="BH5" t="n">
-        <v>73675758.97</v>
+        <v>50086112.28</v>
       </c>
       <c r="BI5" t="n">
-        <v>882846169.6900001</v>
+        <v>1099087044.24</v>
       </c>
       <c r="BJ5" t="n">
         <v>0</v>
       </c>
-      <c r="BK5" t="inlineStr"/>
+      <c r="BK5" t="n">
+        <v>160719000</v>
+      </c>
       <c r="BL5" t="n">
-        <v>274084899.6</v>
+        <v>319320986.63</v>
       </c>
       <c r="BM5" t="n">
-        <v>238790998.52</v>
+        <v>290184536.63</v>
       </c>
       <c r="BN5" t="n">
-        <v>369970271.57</v>
+        <v>328862520.98</v>
       </c>
       <c r="BO5" t="n">
-        <v>1382435761.67</v>
+        <v>241568274.1</v>
       </c>
       <c r="BP5" t="n">
-        <v>1416594832.84</v>
+        <v>1618357551.03</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-144788522.99</v>
+        <v>-165389597.55</v>
       </c>
       <c r="BR5" t="n">
-        <v>1561383355.83</v>
+        <v>1783747148.58</v>
       </c>
       <c r="BS5" t="n">
-        <v>685736443.38</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>2473102</v>
-      </c>
+        <v>731791864.25</v>
+      </c>
+      <c r="BT5" t="inlineStr"/>
       <c r="BU5" t="n">
-        <v>683263341.38</v>
+        <v>731791864.25</v>
       </c>
       <c r="BV5" t="n">
-        <v>350781068.45</v>
+        <v>340432955.98</v>
       </c>
       <c r="BW5" t="n">
-        <v>332482272.93</v>
+        <v>391358908.27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1340000000</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1340000000</v>
-      </c>
-      <c r="D6" t="n">
-        <v>977466987.04</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1904681921.32</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4650812478.51</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7246396567.4</v>
-      </c>
-      <c r="H6" t="n">
-        <v>322144080.51</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4650812478.51</v>
-      </c>
-      <c r="J6" t="n">
-        <v>35677.49</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5395097222.19</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5490205235.89</v>
-      </c>
-      <c r="M6" t="n">
-        <v>5445559336.9</v>
-      </c>
-      <c r="N6" t="n">
-        <v>50462114.71</v>
-      </c>
-      <c r="O6" t="n">
-        <v>5395097222.19</v>
-      </c>
-      <c r="P6" t="n">
-        <v>205142925.63</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>848311577.9299999</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3036005321.44</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1340000000</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1340000000</v>
-      </c>
-      <c r="U6" t="n">
-        <v>4679491912.57</v>
-      </c>
-      <c r="V6" t="n">
-        <v>363964875.35</v>
-      </c>
-      <c r="W6" t="n">
-        <v>56485350.09</v>
-      </c>
-      <c r="X6" t="n">
-        <v>27412920</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>179755037.43</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5167876.64</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>95143691.19</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>35677.49</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>95108013.7</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>4315527037.22</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1938255.56</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1809538230.13</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1756191331.51</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2489140893.42</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>76256102.13</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>34216326.53</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>82053359.86</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2296615104.9</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>10125051249.47</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>5487380131.74</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>291497174.48</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>11410811.61</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>110109739.35</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>117150000</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>117150000</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>552880133.85</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>260455014.68</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>744284743.6799999</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>487779798.66</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>256504945.02</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3091877196.2</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-1891950756.03</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4983827952.23</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>419131988.85</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3926823149.85</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>18820356.64</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>619052456.89</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4637671117.73</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>155332065.32</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>42720183.29</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>932873049.14</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0</v>
-      </c>
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
       <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="n">
-        <v>316922387.24</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>241965741.08</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>373984920.82</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1074642462.71</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1554305066.1</v>
-      </c>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="n">
-        <v>877798291.17</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>3965933</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>873832358.17</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>394584329.02</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>414208061.13</v>
-      </c>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="n">
+        <v>-149134643.84</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1315417481.43</v>
+      </c>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2952,578 +2952,578 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-78451604.36</v>
+        <v>49888237.65</v>
       </c>
       <c r="C2" t="n">
-        <v>-1795269204.16</v>
+        <v>-1758000000</v>
       </c>
       <c r="D2" t="n">
-        <v>2206000000</v>
+        <v>2076700000</v>
       </c>
       <c r="E2" t="n">
-        <v>-542264557.12</v>
+        <v>-91445619.48</v>
       </c>
       <c r="F2" t="n">
-        <v>391358908.27</v>
+        <v>455248029.15</v>
       </c>
       <c r="G2" t="n">
-        <v>433769320.57</v>
+        <v>593499930.86</v>
       </c>
       <c r="H2" t="n">
-        <v>-42410412.3</v>
+        <v>-138251901.71</v>
       </c>
       <c r="I2" t="n">
-        <v>-18704393.29</v>
+        <v>-354937486.09</v>
       </c>
       <c r="J2" t="n">
-        <v>36554541.77</v>
+        <v>-16453670.27</v>
       </c>
       <c r="K2" t="n">
-        <v>-465989730.9</v>
+        <v>-657183815.8200001</v>
       </c>
       <c r="L2" t="n">
-        <v>410730795.84</v>
+        <v>318700000</v>
       </c>
       <c r="M2" t="n">
-        <v>410730795.84</v>
+        <v>318700000</v>
       </c>
       <c r="N2" t="n">
-        <v>-1795269204.16</v>
+        <v>-1758000000</v>
       </c>
       <c r="O2" t="n">
-        <v>2206000000</v>
+        <v>2076700000</v>
       </c>
       <c r="P2" t="n">
-        <v>-487518971.77</v>
+        <v>75351727.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>10000000</v>
+        <v>22315950.15</v>
       </c>
       <c r="R2" t="n">
-        <v>37027705.06</v>
+        <v>73712058.48999999</v>
       </c>
       <c r="S2" t="n">
-        <v>258936005.06</v>
+        <v>291874977.59</v>
       </c>
       <c r="T2" t="n">
-        <v>-221908300</v>
+        <v>-218162919.1</v>
       </c>
       <c r="U2" t="n">
-        <v>4000000</v>
+        <v>49581223.96</v>
       </c>
       <c r="V2" t="n">
-        <v>4000000</v>
+        <v>49581223.96</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>-538546676.83</v>
+        <v>-70257505.34999999</v>
       </c>
       <c r="Y2" t="n">
-        <v>3717880.29</v>
+        <v>21188114.13</v>
       </c>
       <c r="Z2" t="n">
-        <v>-542264557.12</v>
+        <v>-91445619.48</v>
       </c>
       <c r="AA2" t="n">
-        <v>463812952.76</v>
+        <v>141333857.13</v>
       </c>
       <c r="AB2" t="n">
-        <v>-409116336.53</v>
+        <v>-777782597.02</v>
       </c>
       <c r="AC2" t="n">
-        <v>-34652224.99</v>
+        <v>-41751787.09</v>
       </c>
       <c r="AD2" t="n">
-        <v>-394600076.21</v>
+        <v>-590135409.14</v>
       </c>
       <c r="AE2" t="n">
-        <v>-125681466.97</v>
+        <v>-78415458.23</v>
       </c>
       <c r="AF2" t="n">
-        <v>145817431.64</v>
+        <v>-67479942.56</v>
       </c>
       <c r="AG2" t="n">
-        <v>94527140.54000001</v>
+        <v>75624285.70999999</v>
       </c>
       <c r="AH2" t="n">
-        <v>495584956.33</v>
+        <v>515936607.92</v>
       </c>
       <c r="AI2" t="n">
-        <v>52648837.72</v>
+        <v>124206101.29</v>
       </c>
       <c r="AJ2" t="n">
-        <v>442936118.61</v>
+        <v>391730506.63</v>
       </c>
       <c r="AK2" t="n">
-        <v>-12214630.46</v>
+        <v>41533669.29</v>
       </c>
       <c r="AL2" t="n">
-        <v>-2686611.28</v>
+        <v>9365925.279999999</v>
       </c>
       <c r="AM2" t="n">
-        <v>256784458.41</v>
+        <v>-783287743.54</v>
       </c>
       <c r="AN2" t="n">
-        <v>463812952.76</v>
+        <v>141333857.13</v>
       </c>
       <c r="AO2" t="n">
-        <v>-374685865.76</v>
+        <v>-226992583.51</v>
       </c>
       <c r="AP2" t="n">
-        <v>-3668276363.79</v>
+        <v>-3439401667.29</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-186151614.98</v>
+        <v>-194466487.49</v>
       </c>
       <c r="AR2" t="n">
-        <v>-499849014</v>
+        <v>-476322417.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>-2982275734.81</v>
+        <v>-2768612762.79</v>
       </c>
       <c r="AT2" t="n">
-        <v>4506775182.31</v>
+        <v>3807728107.93</v>
       </c>
       <c r="AU2" t="n">
-        <v>260544568.18</v>
+        <v>292615840.67</v>
       </c>
       <c r="AV2" t="n">
-        <v>4246230614.13</v>
+        <v>3515112267.26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>18646072</v>
+        <v>290237761.19</v>
       </c>
       <c r="C3" t="n">
-        <v>-1407000000</v>
+        <v>-2284700000</v>
       </c>
       <c r="D3" t="n">
-        <v>1604000000</v>
+        <v>1971000000</v>
       </c>
       <c r="E3" t="n">
-        <v>-424673779.64</v>
+        <v>-247896209.08</v>
       </c>
       <c r="F3" t="n">
-        <v>433769320.57</v>
+        <v>332482272.93</v>
       </c>
       <c r="G3" t="n">
-        <v>332482272.93</v>
+        <v>455248029.15</v>
       </c>
       <c r="H3" t="n">
-        <v>101287047.64</v>
+        <v>-122765756.22</v>
       </c>
       <c r="I3" t="n">
-        <v>182875233.91</v>
+        <v>-402606305.3</v>
       </c>
       <c r="J3" t="n">
-        <v>40270802.07</v>
+        <v>6850177.3</v>
       </c>
       <c r="K3" t="n">
-        <v>-54395568.16</v>
+        <v>-95756482.59999999</v>
       </c>
       <c r="L3" t="n">
-        <v>197000000</v>
+        <v>-313700000</v>
       </c>
       <c r="M3" t="n">
-        <v>197000000</v>
+        <v>-313700000</v>
       </c>
       <c r="N3" t="n">
-        <v>-1407000000</v>
+        <v>-2284700000</v>
       </c>
       <c r="O3" t="n">
-        <v>1604000000</v>
+        <v>1971000000</v>
       </c>
       <c r="P3" t="n">
-        <v>-524908037.91</v>
+        <v>-258293421.19</v>
       </c>
       <c r="Q3" t="n">
-        <v>8314541.35</v>
+        <v>-2410000</v>
       </c>
       <c r="R3" t="n">
-        <v>-118582874</v>
+        <v>44415377.99</v>
       </c>
       <c r="S3" t="n">
-        <v>188733916.9</v>
+        <v>262446932.69</v>
       </c>
       <c r="T3" t="n">
-        <v>-307316790.9</v>
+        <v>-218031554.7</v>
       </c>
       <c r="U3" t="n">
-        <v>6480783.37</v>
-      </c>
-      <c r="V3" t="n">
-        <v>6480783.37</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>-91850000</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>-91850000</v>
+      </c>
       <c r="X3" t="n">
-        <v>-421120488.63</v>
+        <v>-208448799.18</v>
       </c>
       <c r="Y3" t="n">
-        <v>3553291.01</v>
+        <v>39447409.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>-424673779.64</v>
+        <v>-247896209.08</v>
       </c>
       <c r="AA3" t="n">
-        <v>443319851.64</v>
+        <v>538133970.27</v>
       </c>
       <c r="AB3" t="n">
-        <v>-433954419.88</v>
+        <v>-285336952.63</v>
       </c>
       <c r="AC3" t="n">
-        <v>-53106181.68</v>
+        <v>-27874141.96</v>
       </c>
       <c r="AD3" t="n">
-        <v>-174794803.95</v>
+        <v>243679981.58</v>
       </c>
       <c r="AE3" t="n">
-        <v>-88511092.45</v>
+        <v>44587682.48</v>
       </c>
       <c r="AF3" t="n">
-        <v>-117542341.8</v>
+        <v>-545730474.73</v>
       </c>
       <c r="AG3" t="n">
-        <v>64067342.31</v>
+        <v>68950069.88</v>
       </c>
       <c r="AH3" t="n">
-        <v>441428285.64</v>
+        <v>434791667.28</v>
       </c>
       <c r="AI3" t="n">
-        <v>66392709.39</v>
+        <v>71636607.65000001</v>
       </c>
       <c r="AJ3" t="n">
-        <v>375035576.25</v>
+        <v>363155059.63</v>
       </c>
       <c r="AK3" t="n">
-        <v>-10808710.45</v>
+        <v>-14213949.05</v>
       </c>
       <c r="AL3" t="n">
-        <v>-28997696.35</v>
+        <v>-7966888.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>293708859.64</v>
+        <v>300001490.69</v>
       </c>
       <c r="AN3" t="n">
-        <v>443319851.64</v>
+        <v>538133970.27</v>
       </c>
       <c r="AO3" t="n">
-        <v>-381446484.53</v>
+        <v>-197275005.09</v>
       </c>
       <c r="AP3" t="n">
-        <v>-3573920506.01</v>
+        <v>-2527864186.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-351038395.5</v>
+        <v>-149702870.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>-498333468.03</v>
+        <v>-481746056.73</v>
       </c>
       <c r="AS3" t="n">
-        <v>-2724548642.48</v>
+        <v>-1896415259.29</v>
       </c>
       <c r="AT3" t="n">
-        <v>4398686842.18</v>
+        <v>3263273161.39</v>
       </c>
       <c r="AU3" t="n">
-        <v>141467738.24</v>
+        <v>251914198.26</v>
       </c>
       <c r="AV3" t="n">
-        <v>4257219103.94</v>
+        <v>3011358963.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>290237761.19</v>
+        <v>18646072</v>
       </c>
       <c r="C4" t="n">
-        <v>-2284700000</v>
+        <v>-1407000000</v>
       </c>
       <c r="D4" t="n">
-        <v>1971000000</v>
+        <v>1604000000</v>
       </c>
       <c r="E4" t="n">
-        <v>-247896209.08</v>
+        <v>-424673779.64</v>
       </c>
       <c r="F4" t="n">
+        <v>433769320.57</v>
+      </c>
+      <c r="G4" t="n">
         <v>332482272.93</v>
       </c>
-      <c r="G4" t="n">
-        <v>455248029.15</v>
-      </c>
       <c r="H4" t="n">
-        <v>-122765756.22</v>
+        <v>101287047.64</v>
       </c>
       <c r="I4" t="n">
-        <v>-402606305.3</v>
+        <v>182875233.91</v>
       </c>
       <c r="J4" t="n">
-        <v>6850177.3</v>
+        <v>40270802.07</v>
       </c>
       <c r="K4" t="n">
-        <v>-95756482.59999999</v>
+        <v>-54395568.16</v>
       </c>
       <c r="L4" t="n">
-        <v>-313700000</v>
+        <v>197000000</v>
       </c>
       <c r="M4" t="n">
-        <v>-313700000</v>
+        <v>197000000</v>
       </c>
       <c r="N4" t="n">
-        <v>-2284700000</v>
+        <v>-1407000000</v>
       </c>
       <c r="O4" t="n">
-        <v>1971000000</v>
+        <v>1604000000</v>
       </c>
       <c r="P4" t="n">
-        <v>-258293421.19</v>
+        <v>-524908037.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2410000</v>
+        <v>8314541.35</v>
       </c>
       <c r="R4" t="n">
-        <v>44415377.99</v>
+        <v>-118582874</v>
       </c>
       <c r="S4" t="n">
-        <v>262446932.69</v>
+        <v>188733916.9</v>
       </c>
       <c r="T4" t="n">
-        <v>-218031554.7</v>
+        <v>-307316790.9</v>
       </c>
       <c r="U4" t="n">
-        <v>-91850000</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="n">
-        <v>-91850000</v>
-      </c>
+        <v>6480783.37</v>
+      </c>
+      <c r="V4" t="n">
+        <v>6480783.37</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>-208448799.18</v>
+        <v>-421120488.63</v>
       </c>
       <c r="Y4" t="n">
-        <v>39447409.9</v>
+        <v>3553291.01</v>
       </c>
       <c r="Z4" t="n">
-        <v>-247896209.08</v>
+        <v>-424673779.64</v>
       </c>
       <c r="AA4" t="n">
-        <v>538133970.27</v>
+        <v>443319851.64</v>
       </c>
       <c r="AB4" t="n">
-        <v>-285336952.63</v>
+        <v>-433954419.88</v>
       </c>
       <c r="AC4" t="n">
-        <v>-27874141.96</v>
+        <v>-53106181.68</v>
       </c>
       <c r="AD4" t="n">
-        <v>243679981.58</v>
+        <v>-174794803.95</v>
       </c>
       <c r="AE4" t="n">
-        <v>44587682.48</v>
+        <v>-88511092.45</v>
       </c>
       <c r="AF4" t="n">
-        <v>-545730474.73</v>
+        <v>-117542341.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>68950069.88</v>
+        <v>64067342.31</v>
       </c>
       <c r="AH4" t="n">
-        <v>434791667.28</v>
+        <v>441428285.64</v>
       </c>
       <c r="AI4" t="n">
-        <v>71636607.65000001</v>
+        <v>66392709.39</v>
       </c>
       <c r="AJ4" t="n">
-        <v>363155059.63</v>
+        <v>375035576.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>-14213949.05</v>
+        <v>-10808710.45</v>
       </c>
       <c r="AL4" t="n">
-        <v>-7966888.5</v>
+        <v>-28997696.35</v>
       </c>
       <c r="AM4" t="n">
-        <v>300001490.69</v>
+        <v>293708859.64</v>
       </c>
       <c r="AN4" t="n">
-        <v>538133970.27</v>
+        <v>443319851.64</v>
       </c>
       <c r="AO4" t="n">
-        <v>-197275005.09</v>
+        <v>-381446484.53</v>
       </c>
       <c r="AP4" t="n">
-        <v>-2527864186.03</v>
+        <v>-3573920506.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-149702870.01</v>
+        <v>-351038395.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>-481746056.73</v>
+        <v>-498333468.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1896415259.29</v>
+        <v>-2724548642.48</v>
       </c>
       <c r="AT4" t="n">
-        <v>3263273161.39</v>
+        <v>4398686842.18</v>
       </c>
       <c r="AU4" t="n">
-        <v>251914198.26</v>
+        <v>141467738.24</v>
       </c>
       <c r="AV4" t="n">
-        <v>3011358963.13</v>
+        <v>4257219103.94</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>49888237.65</v>
+        <v>-78451604.36</v>
       </c>
       <c r="C5" t="n">
-        <v>-1758000000</v>
+        <v>-1795269204.16</v>
       </c>
       <c r="D5" t="n">
-        <v>2076700000</v>
+        <v>2206000000</v>
       </c>
       <c r="E5" t="n">
-        <v>-91445619.48</v>
+        <v>-542264557.12</v>
       </c>
       <c r="F5" t="n">
-        <v>455248029.15</v>
+        <v>391358908.27</v>
       </c>
       <c r="G5" t="n">
-        <v>593499930.86</v>
+        <v>433769320.57</v>
       </c>
       <c r="H5" t="n">
-        <v>-138251901.71</v>
+        <v>-42410412.3</v>
       </c>
       <c r="I5" t="n">
-        <v>-354937486.09</v>
+        <v>-18704393.29</v>
       </c>
       <c r="J5" t="n">
-        <v>-16453670.27</v>
+        <v>36554541.77</v>
       </c>
       <c r="K5" t="n">
-        <v>-657183815.8200001</v>
+        <v>-465989730.9</v>
       </c>
       <c r="L5" t="n">
-        <v>318700000</v>
+        <v>410730795.84</v>
       </c>
       <c r="M5" t="n">
-        <v>318700000</v>
+        <v>410730795.84</v>
       </c>
       <c r="N5" t="n">
-        <v>-1758000000</v>
+        <v>-1795269204.16</v>
       </c>
       <c r="O5" t="n">
-        <v>2076700000</v>
+        <v>2206000000</v>
       </c>
       <c r="P5" t="n">
-        <v>75351727.25</v>
+        <v>-487518971.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>22315950.15</v>
+        <v>10000000</v>
       </c>
       <c r="R5" t="n">
-        <v>73712058.48999999</v>
+        <v>37027705.06</v>
       </c>
       <c r="S5" t="n">
-        <v>291874977.59</v>
+        <v>258936005.06</v>
       </c>
       <c r="T5" t="n">
-        <v>-218162919.1</v>
+        <v>-221908300</v>
       </c>
       <c r="U5" t="n">
-        <v>49581223.96</v>
+        <v>4000000</v>
       </c>
       <c r="V5" t="n">
-        <v>49581223.96</v>
+        <v>4000000</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-70257505.34999999</v>
+        <v>-538546676.83</v>
       </c>
       <c r="Y5" t="n">
-        <v>21188114.13</v>
+        <v>3717880.29</v>
       </c>
       <c r="Z5" t="n">
-        <v>-91445619.48</v>
+        <v>-542264557.12</v>
       </c>
       <c r="AA5" t="n">
-        <v>141333857.13</v>
+        <v>463812952.76</v>
       </c>
       <c r="AB5" t="n">
-        <v>-777782597.02</v>
+        <v>-409116336.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>-41751787.09</v>
+        <v>-34652224.99</v>
       </c>
       <c r="AD5" t="n">
-        <v>-590135409.14</v>
+        <v>-394600076.21</v>
       </c>
       <c r="AE5" t="n">
-        <v>-78415458.23</v>
+        <v>-125681466.97</v>
       </c>
       <c r="AF5" t="n">
-        <v>-67479942.56</v>
+        <v>145817431.64</v>
       </c>
       <c r="AG5" t="n">
-        <v>75624285.70999999</v>
+        <v>94527140.54000001</v>
       </c>
       <c r="AH5" t="n">
-        <v>515936607.92</v>
+        <v>495584956.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>124206101.29</v>
+        <v>52648837.72</v>
       </c>
       <c r="AJ5" t="n">
-        <v>391730506.63</v>
+        <v>442936118.61</v>
       </c>
       <c r="AK5" t="n">
-        <v>41533669.29</v>
+        <v>-12214630.46</v>
       </c>
       <c r="AL5" t="n">
-        <v>9365925.279999999</v>
+        <v>-2686611.28</v>
       </c>
       <c r="AM5" t="n">
-        <v>-783287743.54</v>
+        <v>256784458.41</v>
       </c>
       <c r="AN5" t="n">
-        <v>141333857.13</v>
+        <v>463812952.76</v>
       </c>
       <c r="AO5" t="n">
-        <v>-226992583.51</v>
+        <v>-374685865.76</v>
       </c>
       <c r="AP5" t="n">
-        <v>-3439401667.29</v>
+        <v>-3668276363.79</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-194466487.49</v>
+        <v>-186151614.98</v>
       </c>
       <c r="AR5" t="n">
-        <v>-476322417.01</v>
+        <v>-499849014</v>
       </c>
       <c r="AS5" t="n">
-        <v>-2768612762.79</v>
+        <v>-2982275734.81</v>
       </c>
       <c r="AT5" t="n">
-        <v>3807728107.93</v>
+        <v>4506775182.31</v>
       </c>
       <c r="AU5" t="n">
-        <v>292615840.67</v>
+        <v>260544568.18</v>
       </c>
       <c r="AV5" t="n">
-        <v>3515112267.26</v>
+        <v>4246230614.13</v>
       </c>
     </row>
   </sheetData>
@@ -4088,187 +4088,187 @@
       </c>
       <c r="DF1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EQ1" t="inlineStr">
@@ -4368,34 +4368,34 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>7.1</v>
+        <v>6.78</v>
       </c>
       <c r="U2" t="n">
-        <v>7.8</v>
+        <v>6.88</v>
       </c>
       <c r="V2" t="n">
-        <v>6.95</v>
+        <v>6.47</v>
       </c>
       <c r="W2" t="n">
-        <v>7.3</v>
+        <v>6.77</v>
       </c>
       <c r="X2" t="n">
-        <v>7.1</v>
+        <v>6.78</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.8</v>
+        <v>6.88</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.95</v>
+        <v>6.47</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.3</v>
+        <v>6.77</v>
       </c>
       <c r="AB2" t="n">
         <v>0.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AD2" t="n">
         <v>1750291200</v>
@@ -4407,43 +4407,43 @@
         <v>2.31</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.753</v>
+        <v>0.716</v>
       </c>
       <c r="AH2" t="n">
-        <v>47.333332</v>
+        <v>44.266663</v>
       </c>
       <c r="AI2" t="n">
-        <v>15.434782</v>
+        <v>14.434782</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23307961</v>
+        <v>20579161</v>
       </c>
       <c r="AK2" t="n">
-        <v>23307961</v>
+        <v>20579161</v>
       </c>
       <c r="AL2" t="n">
-        <v>19458608</v>
+        <v>21081756</v>
       </c>
       <c r="AM2" t="n">
-        <v>25206514</v>
+        <v>25845960</v>
       </c>
       <c r="AN2" t="n">
-        <v>25206514</v>
+        <v>25845960</v>
       </c>
       <c r="AO2" t="n">
-        <v>7.09</v>
+        <v>6.63</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.1</v>
+        <v>6.64</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9319459840</v>
+        <v>8715664384</v>
       </c>
       <c r="AR2" t="n">
-        <v>9319460000</v>
+        <v>8899428000</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.6</v>
+        <v>6.47</v>
       </c>
       <c r="AT2" t="n">
         <v>11.31</v>
@@ -4455,19 +4455,19 @@
         <v>1.883333</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.8486775</v>
+        <v>1.7289042</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.6682</v>
+        <v>7.4524</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.89725</v>
+        <v>8.805949999999999</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.05</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.007042254</v>
+        <v>0.0073746312</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -4478,13 +4478,13 @@
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>9920820224</v>
+        <v>9317023744</v>
       </c>
       <c r="BE2" t="n">
         <v>0.040510003</v>
       </c>
       <c r="BF2" t="n">
-        <v>650170158</v>
+        <v>649723874</v>
       </c>
       <c r="BG2" t="n">
         <v>1312600000</v>
@@ -4493,7 +4493,7 @@
         <v>0.43582</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.14122</v>
+        <v>0.14124</v>
       </c>
       <c r="BJ2" t="n">
         <v>1312600000</v>
@@ -4502,7 +4502,7 @@
         <v>4.512</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.5735815</v>
+        <v>1.4716312</v>
       </c>
       <c r="BM2" t="n">
         <v>1767139200</v>
@@ -4534,16 +4534,16 @@
         <v>1460332800</v>
       </c>
       <c r="BV2" t="n">
-        <v>1.968</v>
+        <v>1.848</v>
       </c>
       <c r="BW2" t="n">
-        <v>19.118</v>
+        <v>17.955</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.0014104843</v>
+        <v>-0.0029411912</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="BZ2" t="n">
         <v>0.1</v>
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="CC2" t="n">
-        <v>7.1</v>
+        <v>6.64</v>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
@@ -4659,139 +4659,139 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DF2" t="b">
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>1782111879</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>ZHEJIANG WANLIYANG CO LTD</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>Zhejiang Wanliyang Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>finmb_106528429</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="DQ2" t="b">
         <v>0</v>
       </c>
-      <c r="DG2" t="n">
+      <c r="DR2" t="n">
+        <v>-2.0649018</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>21081756</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0.17000008</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.026275128</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>6.47 - 11.31</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
+        <v>-4.6700006</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.41290897</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-0.29411912</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1651143540</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>1651233600</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.8124003400000001</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.1090119</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-2.1659503</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>-0.24596441</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EN2" t="n">
         <v>1276824600000</v>
       </c>
-      <c r="DH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>6.95 - 7.3</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="DK2" t="n">
-        <v>19458608</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0.07575758</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>6.6 - 11.31</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>-4.2100005</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>ZHEJIANG WANLIYANG CO LTD</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>1780038252</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>finmb_106528429</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="EA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.372237</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0.14104843</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>1651143540</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>1651233600</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-0.5682001</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-0.07409824</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>-1.7972503</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>-0.20200065</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
+      <c r="EO2" t="n">
+        <v>-0.14000034</v>
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>Zhejiang Wanliyang Co., Ltd.</t>
+          <t>6.47 - 6.77</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr"/>
